--- a/public/format_upload.xlsx
+++ b/public/format_upload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pongp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC069AA-DEF2-4ACF-A22B-ED70157246B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FEF73C-4306-4A81-A513-3E207F57517B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{047D00F0-D4A0-42CA-9704-2AA10FE2B478}"/>
   </bookViews>
@@ -36,42 +36,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>room_id</t>
-  </si>
-  <si>
-    <t>subject_name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>sec</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>surname</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>start_time</t>
-  </si>
-  <si>
-    <t>end_time</t>
-  </si>
-  <si>
-    <t>repeat</t>
-  </si>
-  <si>
-    <t>ชื่อต้น</t>
-  </si>
-  <si>
     <t>นามสกุล</t>
   </si>
   <si>
     <t>ชื่อวิชา</t>
+  </si>
+  <si>
+    <t>รหัสวิชา</t>
+  </si>
+  <si>
+    <t>ชื่อ</t>
+  </si>
+  <si>
+    <t>วันที่</t>
+  </si>
+  <si>
+    <t>จำนวนสัปดาห์</t>
+  </si>
+  <si>
+    <t>หมายเลขห้อง</t>
+  </si>
+  <si>
+    <t>Advanced Laboratory in Database</t>
+  </si>
+  <si>
+    <t>Data Mining Technologies and Applications</t>
+  </si>
+  <si>
+    <t>Environmental Science and Technology Writing</t>
+  </si>
+  <si>
+    <t>Data Analysis and Visualization</t>
+  </si>
+  <si>
+    <t>Mathematical Packages</t>
+  </si>
+  <si>
+    <t>Mobile Application Design and Development</t>
+  </si>
+  <si>
+    <t>จิรวรรณ</t>
+  </si>
+  <si>
+    <t>เจริญสุข</t>
+  </si>
+  <si>
+    <t>อรวรรณ</t>
+  </si>
+  <si>
+    <t>วัชนุภาพร</t>
+  </si>
+  <si>
+    <t>ชโลธร</t>
+  </si>
+  <si>
+    <t>ชูทอง</t>
+  </si>
+  <si>
+    <t>เฟื่องฟ้า</t>
+  </si>
+  <si>
+    <t>เป็นศิริ</t>
+  </si>
+  <si>
+    <t>วนิดา</t>
+  </si>
+  <si>
+    <t>คำประไพ</t>
+  </si>
+  <si>
+    <t>Pongpak</t>
+  </si>
+  <si>
+    <t>Tepee</t>
+  </si>
+  <si>
+    <t>Supakrit</t>
+  </si>
+  <si>
+    <t>Seekum</t>
+  </si>
+  <si>
+    <t>M-13-15</t>
+  </si>
+  <si>
+    <t>M-16-18</t>
+  </si>
+  <si>
+    <t>F-13-16</t>
+  </si>
+  <si>
+    <t>F-9-12</t>
+  </si>
+  <si>
+    <t>M-10-12</t>
+  </si>
+  <si>
+    <t>Th-13-15</t>
+  </si>
+  <si>
+    <t>Tu-13-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Tu-8-14</t>
   </si>
 </sst>
 </file>
@@ -82,7 +157,7 @@
     <numFmt numFmtId="164" formatCode="[$-1000000]h:mm:ss;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,12 +168,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -111,16 +180,48 @@
       <charset val="222"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Angsana New"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -128,19 +229,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8E4CE693-C1EC-4CB4-9C78-E55E70476EDF}"/>
   </cellStyles>
@@ -477,136 +615,264 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="44.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="7" width="15.42578125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="42" x14ac:dyDescent="0.45">
+      <c r="A2" s="10">
+        <v>26504</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2739327</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>8</v>
       </c>
+      <c r="D2" s="5">
+        <v>870</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="11">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="3" spans="1:9" ht="42" x14ac:dyDescent="0.45">
+      <c r="A3" s="10">
         <v>26504</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="4">
+        <v>2739327</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5">
+        <v>800</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="42" x14ac:dyDescent="0.45">
+      <c r="A4" s="10">
+        <v>26504</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2739435</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5">
+        <v>800</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="42" x14ac:dyDescent="0.45">
+      <c r="A5" s="10">
+        <v>26504</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2739435</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="5">
+        <v>800</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="42" x14ac:dyDescent="0.45">
+      <c r="A6" s="10">
+        <v>26504</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1651341</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5">
+        <v>800</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="42" x14ac:dyDescent="0.45">
+      <c r="A7" s="10">
+        <v>26504</v>
+      </c>
+      <c r="B7" s="4">
+        <v>3651221</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C2">
+      <c r="D7" s="5">
         <v>800</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4">
-        <v>45985</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="I2">
+      <c r="E7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="11">
         <v>15</v>
       </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+    <row r="8" spans="1:9" ht="21" x14ac:dyDescent="0.45">
+      <c r="A8" s="10">
+        <v>26504</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2731372</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5">
+        <v>800</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="11">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+    <row r="9" spans="1:9" ht="42" x14ac:dyDescent="0.45">
+      <c r="A9" s="10">
+        <v>26504</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1418342</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="5">
+        <v>800</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="11">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" display="classlist.php%3fcs=&amp;sm=2&amp;yr=68&amp;seclec=0&amp;seclab=880&amp;css=02739327&amp;cc=1&amp;cn=Advanced Laboratory in Database&amp;c_level=Bachelor" xr:uid="{E67FE72D-42C6-49F1-B274-DB70129B9604}"/>
+    <hyperlink ref="B5" r:id="rId2" display="classlist.php%3fcs=&amp;sm=2&amp;yr=68&amp;seclec=800&amp;seclab=0&amp;css=02739435&amp;cc=3&amp;cn=Data Mining Technologies and Applications&amp;c_level=Bachelor" xr:uid="{5C118D7C-FF99-4EE5-9A5F-DE8BB88ECC01}"/>
+    <hyperlink ref="B6" r:id="rId3" display="classlist.php%3fcs=&amp;sm=2&amp;yr=68&amp;seclec=800&amp;seclab=0&amp;css=01651341&amp;cc=2&amp;cn=Environmental Science and Technology Writing&amp;c_level=Bachelor" xr:uid="{E2068E8A-87C9-4F1D-A53C-DD40ADEC558F}"/>
+    <hyperlink ref="B7" r:id="rId4" display="classlist.php%3fcs=&amp;sm=2&amp;yr=68&amp;seclec=800&amp;seclab=830&amp;css=03651221&amp;cc=3&amp;cn=Data Analysis and Visualization&amp;c_level=Bachelor" xr:uid="{6A331703-AD31-4F56-8006-CF656565064E}"/>
+    <hyperlink ref="B8" r:id="rId5" display="classlist.php%3fcs=&amp;sm=2&amp;yr=68&amp;seclec=800&amp;seclab=830&amp;css=02731372&amp;cc=3&amp;cn=Mathematical Packages&amp;c_level=Bachelor" xr:uid="{8E0B75AF-12EE-4C80-82C8-1E69DBDE9195}"/>
+    <hyperlink ref="B9" r:id="rId6" display="classlist.php%3fcs=&amp;sm=2&amp;yr=68&amp;seclec=800&amp;seclab=830&amp;css=01418342&amp;cc=1&amp;cn=Mobile Application Design and Development&amp;c_level=Bachelor" xr:uid="{E5638408-1A3B-4254-B48F-AAF46D6601A6}"/>
+    <hyperlink ref="B2" r:id="rId7" display="classlist.php%3fcs=&amp;sm=2&amp;yr=68&amp;seclec=0&amp;seclab=830&amp;css=02739327&amp;cc=1&amp;cn=Advanced Laboratory in Database&amp;c_level=Bachelor" xr:uid="{E119696B-F5CB-4387-9041-416A7D539B2B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>